--- a/sub_pro_12_fifa_tm_analysis/datasets/processed_2026/concacaf_fifa_tm_clean_analysis.xlsx
+++ b/sub_pro_12_fifa_tm_analysis/datasets/processed_2026/concacaf_fifa_tm_clean_analysis.xlsx
@@ -1,21 +1,161 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R_Files\sports_data_sci\sub_pro_12_fifa_tm_analysis\datasets\processed_2026\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DAB15BE-88A5-4B56-9647-63C465D04A29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="43">
+  <si>
+    <t>ranking</t>
+  </si>
+  <si>
+    <t>team</t>
+  </si>
+  <si>
+    <t>confederation</t>
+  </si>
+  <si>
+    <t>points</t>
+  </si>
+  <si>
+    <t>squad_size</t>
+  </si>
+  <si>
+    <t>o_age</t>
+  </si>
+  <si>
+    <t>most_valuable_player</t>
+  </si>
+  <si>
+    <t>team_market_value_euros_numeric</t>
+  </si>
+  <si>
+    <t>avg_player_market_value_euros_numeric</t>
+  </si>
+  <si>
+    <t>top_player_value_euros_numeric</t>
+  </si>
+  <si>
+    <t>players_playing_abroad_percent</t>
+  </si>
+  <si>
+    <t>Antigua and Barbuda</t>
+  </si>
+  <si>
+    <t>CONCACAF</t>
+  </si>
+  <si>
+    <t>Luther James-Wildin</t>
+  </si>
+  <si>
+    <t>Bahamas</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Barbados</t>
+  </si>
+  <si>
+    <t>Niall Reid-Stephen</t>
+  </si>
+  <si>
+    <t>Belize</t>
+  </si>
+  <si>
+    <t>Krisean López</t>
+  </si>
+  <si>
+    <t>Cuba</t>
+  </si>
+  <si>
+    <t>Jorge Aguirre</t>
+  </si>
+  <si>
+    <t>Dominica</t>
+  </si>
+  <si>
+    <t>Dominican Republic</t>
+  </si>
+  <si>
+    <t>Pablo Rosario</t>
+  </si>
+  <si>
+    <t>Grenada</t>
+  </si>
+  <si>
+    <t>Regan Charles-Cook</t>
+  </si>
+  <si>
+    <t>Guyana</t>
+  </si>
+  <si>
+    <t>Osaze De Rosario</t>
+  </si>
+  <si>
+    <t>Haiti</t>
+  </si>
+  <si>
+    <t>Wilson Isidor</t>
+  </si>
+  <si>
+    <t>Jamaica</t>
+  </si>
+  <si>
+    <t>Leon Bailey</t>
+  </si>
+  <si>
+    <t>Saint Lucia</t>
+  </si>
+  <si>
+    <t>Arkell Jude-Boyd</t>
+  </si>
+  <si>
+    <t>St. Kitts and Nevis</t>
+  </si>
+  <si>
+    <t>Tyrese Shade</t>
+  </si>
+  <si>
+    <t>St. Vincent and the Grenadines</t>
+  </si>
+  <si>
+    <t>Oalex Anderson</t>
+  </si>
+  <si>
+    <t>Suriname</t>
+  </si>
+  <si>
+    <t>Joël Piroe</t>
+  </si>
+  <si>
+    <t>Trinidad and Tobago</t>
+  </si>
+  <si>
+    <t>Levi García</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -55,7 +195,7 @@
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -63,13 +203,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +255,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +289,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +324,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,80 +500,65 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.54296875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ranking</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>team</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>confederation</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>squad_size</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>o_age</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>most_valuable_player</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>team_market_value_euros_numeric</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>avg_player_market_value_euros_numeric</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>top_player_value_euros_numeric</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>players_playing_abroad_percent</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>165</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Antigua and Barbuda</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>CONCACAF</t>
-        </is>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
       </c>
       <c r="D2">
         <v>986.58</v>
@@ -434,10 +569,8 @@
       <c r="F2">
         <v>23</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Luther James-Wildin</t>
-        </is>
+      <c r="G2" t="s">
+        <v>13</v>
       </c>
       <c r="H2">
         <v>500000</v>
@@ -452,19 +585,15 @@
         <v>39.1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>206</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Bahamas</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CONCACAF</t>
-        </is>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
       </c>
       <c r="D3">
         <v>796.6</v>
@@ -475,28 +604,22 @@
       <c r="F3">
         <v>21.5</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G3" t="s">
+        <v>15</v>
       </c>
       <c r="K3">
         <v>66.7</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>178</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Barbados</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>CONCACAF</t>
-        </is>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
       </c>
       <c r="D4">
         <v>914.42</v>
@@ -507,10 +630,8 @@
       <c r="F4">
         <v>24.6</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Niall Reid-Stephen</t>
-        </is>
+      <c r="G4" t="s">
+        <v>17</v>
       </c>
       <c r="H4">
         <v>200000</v>
@@ -525,19 +646,15 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>181</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Belize</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>CONCACAF</t>
-        </is>
+      <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
       </c>
       <c r="D5">
         <v>910.74</v>
@@ -548,10 +665,8 @@
       <c r="F5">
         <v>26.8</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Krisean López</t>
-        </is>
+      <c r="G5" t="s">
+        <v>19</v>
       </c>
       <c r="H5">
         <v>425000</v>
@@ -566,19 +681,15 @@
         <v>29.2</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>166</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Cuba</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>CONCACAF</t>
-        </is>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
       </c>
       <c r="D6">
         <v>980.49</v>
@@ -589,10 +700,8 @@
       <c r="F6">
         <v>23.8</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Jorge Aguirre</t>
-        </is>
+      <c r="G6" t="s">
+        <v>21</v>
       </c>
       <c r="H6">
         <v>2300000</v>
@@ -607,19 +716,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>183</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Dominica</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CONCACAF</t>
-        </is>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
       </c>
       <c r="D7">
         <v>901.37</v>
@@ -630,28 +735,22 @@
       <c r="F7">
         <v>25.7</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G7" t="s">
+        <v>15</v>
       </c>
       <c r="K7">
         <v>25</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>142</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Dominican Republic</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>CONCACAF</t>
-        </is>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
       </c>
       <c r="D8">
         <v>1077.49</v>
@@ -662,10 +761,8 @@
       <c r="F8">
         <v>24.6</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Pablo Rosario</t>
-        </is>
+      <c r="G8" t="s">
+        <v>24</v>
       </c>
       <c r="H8">
         <v>18850000</v>
@@ -677,22 +774,18 @@
         <v>8000000</v>
       </c>
       <c r="K8">
-        <v>82.59999999999999</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>82.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>164</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Grenada</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>CONCACAF</t>
-        </is>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
       </c>
       <c r="D9">
         <v>989.59</v>
@@ -703,10 +796,8 @@
       <c r="F9">
         <v>25.3</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Regan Charles-Cook</t>
-        </is>
+      <c r="G9" t="s">
+        <v>26</v>
       </c>
       <c r="H9">
         <v>1530000</v>
@@ -721,22 +812,18 @@
         <v>58.5</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>151</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>CONCACAF</t>
-        </is>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
       </c>
       <c r="D10">
-        <v>1041.9</v>
+        <v>1041.9000000000001</v>
       </c>
       <c r="E10">
         <v>26</v>
@@ -744,10 +831,8 @@
       <c r="F10">
         <v>26.1</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Osaze De Rosario</t>
-        </is>
+      <c r="G10" t="s">
+        <v>28</v>
       </c>
       <c r="H10">
         <v>1580000</v>
@@ -762,19 +847,15 @@
         <v>53.8</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>83</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>CONCACAF</t>
-        </is>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
       </c>
       <c r="D11">
         <v>1294.49</v>
@@ -785,10 +866,8 @@
       <c r="F11">
         <v>27.6</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Wilson Isidor</t>
-        </is>
+      <c r="G11" t="s">
+        <v>30</v>
       </c>
       <c r="H11">
         <v>55100000</v>
@@ -803,19 +882,15 @@
         <v>96</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>70</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Jamaica</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>CONCACAF</t>
-        </is>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
       </c>
       <c r="D12">
         <v>1362.4</v>
@@ -826,10 +901,8 @@
       <c r="F12">
         <v>27.5</v>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Leon Bailey</t>
-        </is>
+      <c r="G12" t="s">
+        <v>32</v>
       </c>
       <c r="H12">
         <v>53680000</v>
@@ -841,22 +914,18 @@
         <v>16000000</v>
       </c>
       <c r="K12">
-        <v>92.59999999999999</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>92.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>167</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Saint Lucia</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>CONCACAF</t>
-        </is>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
       </c>
       <c r="D13">
         <v>980.28</v>
@@ -867,10 +936,8 @@
       <c r="F13">
         <v>26.6</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Arkell Jude-Boyd</t>
-        </is>
+      <c r="G13" t="s">
+        <v>34</v>
       </c>
       <c r="H13">
         <v>500000</v>
@@ -885,19 +952,15 @@
         <v>66.7</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>154</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>St. Kitts and Nevis</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>CONCACAF</t>
-        </is>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
       </c>
       <c r="D14">
         <v>1035.25</v>
@@ -908,10 +971,8 @@
       <c r="F14">
         <v>27.4</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Tyrese Shade</t>
-        </is>
+      <c r="G14" t="s">
+        <v>36</v>
       </c>
       <c r="H14">
         <v>575000</v>
@@ -926,19 +987,15 @@
         <v>60.9</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>171</v>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>St. Vincent and the Grenadines</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>CONCACAF</t>
-        </is>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
       </c>
       <c r="D15">
         <v>963.74</v>
@@ -949,10 +1006,8 @@
       <c r="F15">
         <v>25</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Oalex Anderson</t>
-        </is>
+      <c r="G15" t="s">
+        <v>38</v>
       </c>
       <c r="H15">
         <v>425000</v>
@@ -967,19 +1022,15 @@
         <v>40.6</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>123</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Suriname</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>CONCACAF</t>
-        </is>
+      <c r="B16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
       </c>
       <c r="D16">
         <v>1140.54</v>
@@ -990,10 +1041,8 @@
       <c r="F16">
         <v>28.9</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Joël Piroe</t>
-        </is>
+      <c r="G16" t="s">
+        <v>40</v>
       </c>
       <c r="H16">
         <v>37700000</v>
@@ -1008,19 +1057,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>97</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Trinidad and Tobago</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>CONCACAF</t>
-        </is>
+      <c r="B17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
       </c>
       <c r="D17">
         <v>1227.32</v>
@@ -1031,10 +1076,8 @@
       <c r="F17">
         <v>24.9</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Levi García</t>
-        </is>
+      <c r="G17" t="s">
+        <v>42</v>
       </c>
       <c r="H17">
         <v>1100000</v>
